--- a/data/processed/harmonization/Acidity__Soil_pH/10.15485_3030227/10.15485_3030227_soil_Acidity__Soil_pH.xlsx
+++ b/data/processed/harmonization/Acidity__Soil_pH/10.15485_3030227/10.15485_3030227_soil_Acidity__Soil_pH.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0209</t>
+          <t>upland:10.58052/IEEXG0209</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020N</t>
+          <t>transition:10.58052/IEEXG020N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0211</t>
+          <t>wetland:10.58052/IEEXG0211</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021F</t>
+          <t>upland:10.58052/IEEXG021F</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021T</t>
+          <t>transition:10.58052/IEEXG021T</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0227</t>
+          <t>wetland:10.58052/IEEXG0227</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022L</t>
+          <t>upland:10.58052/IEEXG022L</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022Z</t>
+          <t>transition:10.58052/IEEXG022Z</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023D</t>
+          <t>wetland:10.58052/IEEXG023D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023R</t>
+          <t>upland:10.58052/IEEXG023R</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0245</t>
+          <t>transition:10.58052/IEEXG0245</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024J</t>
+          <t>wetland:10.58052/IEEXG024J</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024X</t>
+          <t>upland:10.58052/IEEXG024X</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025B</t>
+          <t>transition:10.58052/IEEXG025B</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025P</t>
+          <t>wetland:10.58052/IEEXG025P</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0263</t>
+          <t>upland:10.58052/IEEXG0263</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026H</t>
+          <t>transition:10.58052/IEEXG026H</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026V</t>
+          <t>wetland:10.58052/IEEXG026V</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0279</t>
+          <t>upland:10.58052/IEEXG0279</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027N</t>
+          <t>transition:10.58052/IEEXG027N</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028F</t>
+          <t>upland:10.58052/IEEXG028F</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028T</t>
+          <t>transition:10.58052/IEEXG028T</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0297</t>
+          <t>wetland:10.58052/IEEXG0297</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AR</t>
+          <t>upland:10.58052/IEEXG02AR</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02B5</t>
+          <t>transition:10.58052/IEEXG02B5</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BJ</t>
+          <t>wetland:10.58052/IEEXG02BJ</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BX</t>
+          <t>upland:10.58052/IEEXG02BX</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CB</t>
+          <t>transition:10.58052/IEEXG02CB</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CP</t>
+          <t>wetland:10.58052/IEEXG02CP</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02D3</t>
+          <t>upland:10.58052/IEEXG02D3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DH</t>
+          <t>transition:10.58052/IEEXG02DH</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DV</t>
+          <t>wetland:10.58052/IEEXG02DV</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02E9</t>
+          <t>upland:10.58052/IEEXG02E9</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EN</t>
+          <t>transition:10.58052/IEEXG02EN</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02F1</t>
+          <t>wetland:10.58052/IEEXG02F1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FF</t>
+          <t>upland:10.58052/IEEXG02FF</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FT</t>
+          <t>transition:10.58052/IEEXG02FT</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02G7</t>
+          <t>wetland:10.58052/IEEXG02G7</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GL</t>
+          <t>upland:10.58052/IEEXG02GL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GZ</t>
+          <t>transition:10.58052/IEEXG02GZ</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HD</t>
+          <t>wetland:10.58052/IEEXG02HD</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HR</t>
+          <t>upland:10.58052/IEEXG02HR</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02I5</t>
+          <t>transition:10.58052/IEEXG02I5</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IJ</t>
+          <t>wetland:10.58052/IEEXG02IJ</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02K3</t>
+          <t>upland:10.58052/IEEXG02K3</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KH</t>
+          <t>transition:10.58052/IEEXG02KH</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KV</t>
+          <t>wetland:10.58052/IEEXG02KV</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02L9</t>
+          <t>upland:10.58052/IEEXG02L9</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LN</t>
+          <t>transition:10.58052/IEEXG02LN</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02M1</t>
+          <t>wetland:10.58052/IEEXG02M1</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2918,12 +2918,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MF</t>
+          <t>upland:10.58052/IEEXG02MF</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MT</t>
+          <t>transition:10.58052/IEEXG02MT</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02N7</t>
+          <t>wetland:10.58052/IEEXG02N7</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -3062,12 +3062,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NL</t>
+          <t>upland:10.58052/IEEXG02NL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NZ</t>
+          <t>transition:10.58052/IEEXG02NZ</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OD</t>
+          <t>wetland:10.58052/IEEXG02OD</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OR</t>
+          <t>upland:10.58052/IEEXG02OR</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02P5</t>
+          <t>transition:10.58052/IEEXG02P5</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PJ</t>
+          <t>wetland:10.58052/IEEXG02PJ</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PX</t>
+          <t>upland:10.58052/IEEXG02PX</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QB</t>
+          <t>transition:10.58052/IEEXG02QB</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QP</t>
+          <t>wetland:10.58052/IEEXG02QP</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02S9</t>
+          <t>upland:10.58052/IEEXG02S9</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SN</t>
+          <t>transition:10.58052/IEEXG02SN</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02T1</t>
+          <t>wetland:10.58052/IEEXG02T1</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TF</t>
+          <t>upland:10.58052/IEEXG02TF</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TT</t>
+          <t>transition:10.58052/IEEXG02TT</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02U7</t>
+          <t>wetland:10.58052/IEEXG02U7</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UL</t>
+          <t>upland:10.58052/IEEXG02UL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UZ</t>
+          <t>transition:10.58052/IEEXG02UZ</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VD</t>
+          <t>wetland:10.58052/IEEXG02VD</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VR</t>
+          <t>upland:10.58052/IEEXG02VR</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02W5</t>
+          <t>transition:10.58052/IEEXG02W5</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WJ</t>
+          <t>wetland:10.58052/IEEXG02WJ</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WX</t>
+          <t>upland:10.58052/IEEXG02WX</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4118,12 +4118,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02XB</t>
+          <t>transition:10.58052/IEEXG02XB</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02XP</t>
+          <t>wetland:10.58052/IEEXG02XP</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Y3</t>
+          <t>upland:10.58052/IEEXG02Y3</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YH</t>
+          <t>transition:10.58052/IEEXG02YH</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YV</t>
+          <t>wetland:10.58052/IEEXG02YV</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Z9</t>
+          <t>upland:10.58052/IEEXG02Z9</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZN</t>
+          <t>transition:10.58052/IEEXG02ZN</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0301</t>
+          <t>wetland:10.58052/IEEXG0301</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -4502,12 +4502,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030F</t>
+          <t>upland:10.58052/IEEXG030F</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030T</t>
+          <t>transition:10.58052/IEEXG030T</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0317</t>
+          <t>wetland:10.58052/IEEXG0317</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031L</t>
+          <t>upland:10.58052/IEEXG031L</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031Z</t>
+          <t>transition:10.58052/IEEXG031Z</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032D</t>
+          <t>wetland:10.58052/IEEXG032D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -4790,12 +4790,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032R</t>
+          <t>upland:10.58052/IEEXG032R</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0335</t>
+          <t>transition:10.58052/IEEXG0335</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG033J</t>
+          <t>wetland:10.58052/IEEXG033J</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0353</t>
+          <t>upland:10.58052/IEEXG0353</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -4982,12 +4982,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035H</t>
+          <t>transition:10.58052/IEEXG035H</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -5030,12 +5030,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG035V</t>
+          <t>wetland:10.58052/IEEXG035V</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020A</t>
+          <t>upland:10.58052/IEEXG020A</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -5126,12 +5126,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG020O</t>
+          <t>transition:10.58052/IEEXG020O</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0212</t>
+          <t>wetland:10.58052/IEEXG0212</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021G</t>
+          <t>upland:10.58052/IEEXG021G</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG021U</t>
+          <t>transition:10.58052/IEEXG021U</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0228</t>
+          <t>wetland:10.58052/IEEXG0228</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -5366,12 +5366,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG022M</t>
+          <t>upland:10.58052/IEEXG022M</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0230</t>
+          <t>transition:10.58052/IEEXG0230</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -5462,12 +5462,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023E</t>
+          <t>wetland:10.58052/IEEXG023E</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG023S</t>
+          <t>upland:10.58052/IEEXG023S</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0246</t>
+          <t>transition:10.58052/IEEXG0246</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024K</t>
+          <t>wetland:10.58052/IEEXG024K</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG024Y</t>
+          <t>upland:10.58052/IEEXG024Y</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -5702,12 +5702,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025C</t>
+          <t>transition:10.58052/IEEXG025C</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG025Q</t>
+          <t>wetland:10.58052/IEEXG025Q</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -5798,12 +5798,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0264</t>
+          <t>upland:10.58052/IEEXG0264</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026I</t>
+          <t>transition:10.58052/IEEXG026I</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -5894,12 +5894,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG026W</t>
+          <t>wetland:10.58052/IEEXG026W</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -5942,12 +5942,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027A</t>
+          <t>upland:10.58052/IEEXG027A</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -5990,12 +5990,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG027O</t>
+          <t>transition:10.58052/IEEXG027O</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -6038,12 +6038,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0282</t>
+          <t>wetland:10.58052/IEEXG0282</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028G</t>
+          <t>upland:10.58052/IEEXG028G</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG028U</t>
+          <t>transition:10.58052/IEEXG028U</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0298</t>
+          <t>wetland:10.58052/IEEXG0298</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -6230,12 +6230,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG029M</t>
+          <t>upland:10.58052/IEEXG029M</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -6278,12 +6278,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02A0</t>
+          <t>transition:10.58052/IEEXG02A0</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AE</t>
+          <t>wetland:10.58052/IEEXG02AE</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02AS</t>
+          <t>upland:10.58052/IEEXG02AS</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02B6</t>
+          <t>transition:10.58052/IEEXG02B6</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -6470,12 +6470,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BK</t>
+          <t>wetland:10.58052/IEEXG02BK</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -6518,12 +6518,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02BY</t>
+          <t>upland:10.58052/IEEXG02BY</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -6566,12 +6566,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CC</t>
+          <t>transition:10.58052/IEEXG02CC</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02CQ</t>
+          <t>wetland:10.58052/IEEXG02CQ</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02D4</t>
+          <t>upland:10.58052/IEEXG02D4</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -6710,12 +6710,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DI</t>
+          <t>transition:10.58052/IEEXG02DI</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02DW</t>
+          <t>wetland:10.58052/IEEXG02DW</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EA</t>
+          <t>upland:10.58052/IEEXG02EA</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02EO</t>
+          <t>transition:10.58052/IEEXG02EO</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -6902,12 +6902,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02F2</t>
+          <t>wetland:10.58052/IEEXG02F2</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FG</t>
+          <t>upland:10.58052/IEEXG02FG</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02FU</t>
+          <t>transition:10.58052/IEEXG02FU</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -7046,12 +7046,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02G8</t>
+          <t>wetland:10.58052/IEEXG02G8</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02GM</t>
+          <t>upland:10.58052/IEEXG02GM</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -7142,12 +7142,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02H0</t>
+          <t>transition:10.58052/IEEXG02H0</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HE</t>
+          <t>wetland:10.58052/IEEXG02HE</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02HS</t>
+          <t>upland:10.58052/IEEXG02HS</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02I6</t>
+          <t>transition:10.58052/IEEXG02I6</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IK</t>
+          <t>wetland:10.58052/IEEXG02IK</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -7382,12 +7382,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02IY</t>
+          <t>upland:10.58052/IEEXG02IY</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -7430,12 +7430,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JC</t>
+          <t>transition:10.58052/IEEXG02JC</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02JQ</t>
+          <t>wetland:10.58052/IEEXG02JQ</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02K4</t>
+          <t>upland:10.58052/IEEXG02K4</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KI</t>
+          <t>transition:10.58052/IEEXG02KI</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -7622,12 +7622,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02KW</t>
+          <t>wetland:10.58052/IEEXG02KW</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -7670,12 +7670,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LA</t>
+          <t>upland:10.58052/IEEXG02LA</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02LO</t>
+          <t>transition:10.58052/IEEXG02LO</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02M2</t>
+          <t>wetland:10.58052/IEEXG02M2</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MG</t>
+          <t>upland:10.58052/IEEXG02MG</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -7862,12 +7862,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02MU</t>
+          <t>transition:10.58052/IEEXG02MU</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -7910,12 +7910,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02N8</t>
+          <t>wetland:10.58052/IEEXG02N8</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -7958,12 +7958,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02NM</t>
+          <t>upland:10.58052/IEEXG02NM</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -8006,12 +8006,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02O0</t>
+          <t>transition:10.58052/IEEXG02O0</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OE</t>
+          <t>wetland:10.58052/IEEXG02OE</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -8102,12 +8102,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02OS</t>
+          <t>upland:10.58052/IEEXG02OS</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -8150,12 +8150,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02P6</t>
+          <t>transition:10.58052/IEEXG02P6</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -8198,12 +8198,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PK</t>
+          <t>wetland:10.58052/IEEXG02PK</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -8246,12 +8246,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02PY</t>
+          <t>upland:10.58052/IEEXG02PY</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QC</t>
+          <t>transition:10.58052/IEEXG02QC</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -8342,12 +8342,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02QQ</t>
+          <t>wetland:10.58052/IEEXG02QQ</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -8390,12 +8390,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SA</t>
+          <t>upland:10.58052/IEEXG02SA</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -8438,12 +8438,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02SO</t>
+          <t>transition:10.58052/IEEXG02SO</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -8486,12 +8486,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02T2</t>
+          <t>wetland:10.58052/IEEXG02T2</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -8534,12 +8534,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TG</t>
+          <t>upland:10.58052/IEEXG02TG</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02TU</t>
+          <t>transition:10.58052/IEEXG02TU</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02U8</t>
+          <t>wetland:10.58052/IEEXG02U8</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02UM</t>
+          <t>upland:10.58052/IEEXG02UM</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -8726,12 +8726,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02V0</t>
+          <t>transition:10.58052/IEEXG02V0</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VE</t>
+          <t>wetland:10.58052/IEEXG02VE</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02VS</t>
+          <t>upland:10.58052/IEEXG02VS</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -8870,12 +8870,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02W6</t>
+          <t>transition:10.58052/IEEXG02W6</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02WK</t>
+          <t>wetland:10.58052/IEEXG02WK</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -8966,12 +8966,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02Y4</t>
+          <t>upland:10.58052/IEEXG02Y4</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YI</t>
+          <t>transition:10.58052/IEEXG02YI</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -9062,12 +9062,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02YW</t>
+          <t>wetland:10.58052/IEEXG02YW</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZA</t>
+          <t>upland:10.58052/IEEXG02ZA</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -9158,12 +9158,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG02ZO</t>
+          <t>transition:10.58052/IEEXG02ZO</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0302</t>
+          <t>wetland:10.58052/IEEXG0302</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
@@ -9254,12 +9254,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030G</t>
+          <t>upland:10.58052/IEEXG030G</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
@@ -9302,12 +9302,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG030U</t>
+          <t>transition:10.58052/IEEXG030U</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -9350,12 +9350,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0318</t>
+          <t>wetland:10.58052/IEEXG0318</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -9398,12 +9398,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG031M</t>
+          <t>upland:10.58052/IEEXG031M</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -9446,12 +9446,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0320</t>
+          <t>transition:10.58052/IEEXG0320</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032E</t>
+          <t>wetland:10.58052/IEEXG032E</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG032S</t>
+          <t>upland:10.58052/IEEXG032S</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -9590,12 +9590,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG0336</t>
+          <t>transition:10.58052/IEEXG0336</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>10.58052/IEEXG033K</t>
+          <t>wetland:10.58052/IEEXG033K</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
